--- a/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497638357014</v>
+        <v>10.84497641835961</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907212085509</v>
+        <v>37.7890722420782</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.108434215823654</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="C2" t="n">
-        <v>3.808199344773377</v>
+        <v>9.669233139126835</v>
       </c>
       <c r="D2" t="n">
-        <v>28.41079681319844</v>
+        <v>26.00355144238527</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.77945092390974</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03104037810418</v>
+        <v>42.05807164993336</v>
       </c>
       <c r="D3" t="n">
-        <v>78.02439879501526</v>
+        <v>89.81027998449821</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.08395694314227</v>
+        <v>29.85200244303276</v>
       </c>
       <c r="C4" t="n">
-        <v>62.01405723415827</v>
+        <v>75.74674412116265</v>
       </c>
       <c r="D4" t="n">
-        <v>92.46590752448584</v>
+        <v>108.9298165247048</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.17297718905925</v>
+        <v>38.14089830998859</v>
       </c>
       <c r="C5" t="n">
-        <v>98.17477042468106</v>
+        <v>106.2741889847172</v>
       </c>
       <c r="D5" t="n">
-        <v>69.11503837897546</v>
+        <v>70.73492209098271</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.33215918586747</v>
+        <v>37.07177506006381</v>
       </c>
       <c r="C6" t="n">
-        <v>128.0405173355733</v>
+        <v>133.7562524696982</v>
       </c>
       <c r="D6" t="n">
-        <v>48.70450360768427</v>
+        <v>46.65166915810419</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.17044855210722</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>128.7562114119692</v>
+        <v>146.1832149100543</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>38.86640986342697</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="C8" t="n">
-        <v>93.79617566374026</v>
+        <v>106.647253112331</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>50.47655821384974</v>
+        <v>55.57968278052466</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.664733289781937</v>
+        <v>7.646736221778488</v>
       </c>
       <c r="C21" t="n">
-        <v>93.89298279982873</v>
+        <v>92.71667668906416</v>
       </c>
       <c r="D21" t="n">
-        <v>7.664733289781937</v>
+        <v>7.646736221778488</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.030876147188157</v>
+        <v>5.850234569606743</v>
       </c>
       <c r="C2" t="n">
-        <v>8.144578954431539</v>
+        <v>14.59269787592459</v>
       </c>
       <c r="D2" t="n">
-        <v>29.17066953628548</v>
+        <v>31.23921194913351</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.95263943048468</v>
+        <v>16.23810702824224</v>
       </c>
       <c r="C3" t="n">
-        <v>20.20436775339936</v>
+        <v>39.55952374262523</v>
       </c>
       <c r="D3" t="n">
-        <v>81.48505945248526</v>
+        <v>89.06415172927063</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.60798923303181</v>
+        <v>28.60125586782233</v>
       </c>
       <c r="C4" t="n">
-        <v>62.79258316362599</v>
+        <v>89.64534637018475</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6663072293392</v>
+        <v>123.6962837442811</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.98354093986863</v>
+        <v>40.76707341884881</v>
       </c>
       <c r="C5" t="n">
-        <v>105.8324025178062</v>
+        <v>120.4358996184775</v>
       </c>
       <c r="D5" t="n">
-        <v>83.03131208667401</v>
+        <v>89.8790023237955</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.636583089642</v>
+        <v>43.27053006467818</v>
       </c>
       <c r="C6" t="n">
-        <v>140.0757624419349</v>
+        <v>149.9776697869682</v>
       </c>
       <c r="D6" t="n">
-        <v>57.9623844587317</v>
+        <v>55.54728510628455</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.93196597543326</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>155.8848457234213</v>
+        <v>166.9039819558875</v>
       </c>
       <c r="D7" t="n">
-        <v>43.71722527011047</v>
+        <v>42.93869934064274</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.5283444958008</v>
+        <v>19.77730750205199</v>
       </c>
       <c r="C8" t="n">
-        <v>128.8445687053514</v>
+        <v>146.5356623358789</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>80.98436812331937</v>
+        <v>88.74999246391164</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>44.55661955724149</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.840843909903987</v>
+        <v>7.816791094585173</v>
       </c>
       <c r="C21" t="n">
-        <v>101.9309708287519</v>
+        <v>100.6411853427841</v>
       </c>
       <c r="D21" t="n">
-        <v>8.820949398641986</v>
+        <v>8.79388998140832</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.516841260790327</v>
+        <v>6.066219064541041</v>
       </c>
       <c r="C2" t="n">
-        <v>8.295768100885548</v>
+        <v>12.12556589515235</v>
       </c>
       <c r="D2" t="n">
-        <v>26.82625601854409</v>
+        <v>28.68863141350029</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.09499284760046</v>
+        <v>17.27385085622263</v>
       </c>
       <c r="C3" t="n">
-        <v>25.32418203104648</v>
+        <v>46.74591693771188</v>
       </c>
       <c r="D3" t="n">
-        <v>83.99342483683586</v>
+        <v>91.41543748094176</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.94432778496097</v>
+        <v>28.77993394999525</v>
       </c>
       <c r="C4" t="n">
-        <v>57.04935909378215</v>
+        <v>92.36380576324416</v>
       </c>
       <c r="D4" t="n">
-        <v>118.361466719404</v>
+        <v>135.4635117273834</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.20443417332415</v>
+        <v>41.62610266006477</v>
       </c>
       <c r="C5" t="n">
-        <v>108.7531019379404</v>
+        <v>138.8682127657113</v>
       </c>
       <c r="D5" t="n">
-        <v>98.34657627292425</v>
+        <v>106.1514705216864</v>
       </c>
     </row>
     <row r="6">
@@ -1458,10 +1458,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.44540432922113</v>
+        <v>47.53720558733482</v>
       </c>
       <c r="C6" t="n">
-        <v>150.9437095279471</v>
+        <v>165.4745572985042</v>
       </c>
       <c r="D6" t="n">
         <v>67.13976199803088</v>
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.87314322863646</v>
+        <v>40.48334833232147</v>
       </c>
       <c r="C7" t="n">
-        <v>176.9050458190497</v>
+        <v>186.6665632423758</v>
       </c>
       <c r="D7" t="n">
-        <v>49.0471335564664</v>
+        <v>47.13076203777662</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.28906009787184</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="C8" t="n">
-        <v>161.3060565462722</v>
+        <v>177.0778334149972</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.31093628480575</v>
+        <v>13.7562488319063</v>
       </c>
       <c r="C9" t="n">
-        <v>113.7109278443868</v>
+        <v>127.1343642045534</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>66.05198554172541</v>
+        <v>69.46846755250431</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>40.33706792438868</v>
+        <v>41.40324593120072</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1584,7 +1584,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>24.36697801940583</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001685226976386</v>
+        <v>7.969808759854629</v>
       </c>
       <c r="C21" t="n">
-        <v>110.0231718709253</v>
+        <v>107.5924182580375</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00210653372048</v>
+        <v>9.962260949818287</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.068182559949535</v>
+        <v>5.682355712180538</v>
       </c>
       <c r="C2" t="n">
-        <v>5.706899404786709</v>
+        <v>8.536296288426016</v>
       </c>
       <c r="D2" t="n">
-        <v>22.2670196800219</v>
+        <v>23.82799852977434</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.48831382410494</v>
+        <v>20.0227444281137</v>
       </c>
       <c r="C3" t="n">
-        <v>38.0132711084365</v>
+        <v>66.04216806468294</v>
       </c>
       <c r="D3" t="n">
-        <v>90.58586067085321</v>
+        <v>99.37250262386215</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.07874510498477</v>
+        <v>19.99918248321178</v>
       </c>
       <c r="C4" t="n">
-        <v>85.49746231974197</v>
+        <v>118.0806868759894</v>
       </c>
       <c r="D4" t="n">
-        <v>112.6054799294049</v>
+        <v>127.1039300257218</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.91309178487433</v>
+        <v>26.77716863333176</v>
       </c>
       <c r="C5" t="n">
-        <v>90.19807032767571</v>
+        <v>98.86199381765383</v>
       </c>
       <c r="D5" t="n">
-        <v>66.53795065532759</v>
+        <v>67.61787312999908</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.45792070300229</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C6" t="n">
-        <v>116.4882920997011</v>
+        <v>122.9285570395601</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>113.425239262451</v>
+        <v>124.5042621048762</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>28.02693346083794</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>83.7823490804228</v>
+        <v>93.71272710887928</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.45319189093031</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>53.0281204971872</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>27.8983245115816</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1881,7 +1881,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>20.28094407433061</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.84452400983051</v>
+        <v>3.563744166415922</v>
       </c>
       <c r="C2" t="n">
-        <v>2.838232612977529</v>
+        <v>5.048146695237099</v>
       </c>
       <c r="D2" t="n">
-        <v>16.00543282233575</v>
+        <v>16.83010089390307</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.91399141712056</v>
+        <v>20.23382018452676</v>
       </c>
       <c r="C3" t="n">
-        <v>30.61580215693678</v>
+        <v>50.96252332745193</v>
       </c>
       <c r="D3" t="n">
-        <v>89.0592429907494</v>
+        <v>96.33399347921828</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.70634392990574</v>
+        <v>27.31222113214627</v>
       </c>
       <c r="C4" t="n">
-        <v>93.14233169271189</v>
+        <v>142.6999740553866</v>
       </c>
       <c r="D4" t="n">
-        <v>127.9590322761208</v>
+        <v>144.5760939182023</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.71736413883072</v>
+        <v>29.30516897176729</v>
       </c>
       <c r="C5" t="n">
-        <v>121.6876279413922</v>
+        <v>151.9990883100124</v>
       </c>
       <c r="D5" t="n">
-        <v>84.50393364304422</v>
+        <v>87.22828352232911</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.17365583712723</v>
+        <v>29.46421209985528</v>
       </c>
       <c r="C6" t="n">
-        <v>134.4405306195582</v>
+        <v>143.2556432559903</v>
       </c>
       <c r="D6" t="n">
-        <v>40.21140421824511</v>
+        <v>38.44033135978387</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>138.0985225655818</v>
+        <v>148.5187926984575</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>30.60205768907732</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>108.9003640935774</v>
+        <v>119.9155733352267</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>55.91249525226433</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,10 +2150,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>29.14219885286231</v>
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.605779391249286</v>
+        <v>2.855904071653971</v>
       </c>
       <c r="C2" t="n">
-        <v>6.336199683208914</v>
+        <v>4.51211244871834</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39773099340697</v>
+        <v>20.73352976598839</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.12797135891735</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C3" t="n">
-        <v>20.30254252382404</v>
+        <v>34.8422260237193</v>
       </c>
       <c r="D3" t="n">
-        <v>81.84339736453535</v>
+        <v>89.12796533004668</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.32644862609123</v>
+        <v>32.13652935081509</v>
       </c>
       <c r="C4" t="n">
-        <v>84.56578374841175</v>
+        <v>134.9274774808646</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9642441142783</v>
+        <v>155.0542871656285</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.245986372072</v>
+        <v>34.41025703385071</v>
       </c>
       <c r="C5" t="n">
-        <v>146.1576894697439</v>
+        <v>205.5288818840698</v>
       </c>
       <c r="D5" t="n">
-        <v>106.7405191442345</v>
+        <v>113.88273369263</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.49945720621693</v>
+        <v>33.85164259013428</v>
       </c>
       <c r="C6" t="n">
-        <v>163.8242394076653</v>
+        <v>186.687179944165</v>
       </c>
       <c r="D6" t="n">
-        <v>53.81646390369741</v>
+        <v>52.97117913034091</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.40999499194344</v>
+        <v>23.41566449399068</v>
       </c>
       <c r="C7" t="n">
-        <v>166.0655694164607</v>
+        <v>176.4858395493364</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>143.4480658060227</v>
+        <v>154.2963779379499</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>89.08280493565131</v>
+        <v>92.85467961536754</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2461,10 +2461,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.295727043156542</v>
+        <v>1.731802950291373</v>
       </c>
       <c r="C2" t="n">
-        <v>2.965859814529614</v>
+        <v>2.240348261091221</v>
       </c>
       <c r="D2" t="n">
-        <v>10.77075406329176</v>
+        <v>14.618223316235</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78221624057323</v>
+        <v>15.4821612959722</v>
       </c>
       <c r="C3" t="n">
-        <v>23.50794877818987</v>
+        <v>29.78131660832699</v>
       </c>
       <c r="D3" t="n">
-        <v>79.50192908990671</v>
+        <v>88.66654390905069</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.42328179591317</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>80.54552689952106</v>
+        <v>132.745052334324</v>
       </c>
       <c r="D4" t="n">
-        <v>150.1789280663388</v>
+        <v>164.8050053642078</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.03767593232243</v>
+        <v>35.85833489761475</v>
       </c>
       <c r="C5" t="n">
-        <v>171.1186248502191</v>
+        <v>247.6213147036518</v>
       </c>
       <c r="D5" t="n">
-        <v>112.7782675253524</v>
+        <v>116.6561709571273</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>27.65288758551991</v>
       </c>
       <c r="C6" t="n">
-        <v>201.2985310264703</v>
+        <v>218.6872463640898</v>
       </c>
       <c r="D6" t="n">
-        <v>52.64916588334796</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>180.2586959767568</v>
+        <v>189.4213473004923</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>109.2341583130213</v>
+        <v>112.2383062880166</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,10 +2758,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.20360698987336</v>
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.200497515844602</v>
+        <v>1.829977720716055</v>
       </c>
       <c r="C2" t="n">
-        <v>5.630323083855457</v>
+        <v>2.87161203492192</v>
       </c>
       <c r="D2" t="n">
-        <v>9.867546175384691</v>
+        <v>15.71974424039993</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.51652246562084</v>
+        <v>11.01030050312798</v>
       </c>
       <c r="C3" t="n">
-        <v>17.33275571847744</v>
+        <v>19.45333075965055</v>
       </c>
       <c r="D3" t="n">
-        <v>70.67110849020665</v>
+        <v>80.85183218324607</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.64926369433918</v>
+        <v>32.36625831360885</v>
       </c>
       <c r="C4" t="n">
-        <v>70.30982533504381</v>
+        <v>106.3006961727319</v>
       </c>
       <c r="D4" t="n">
-        <v>154.8373209229899</v>
+        <v>169.8845679859808</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.30890034060182</v>
+        <v>42.68148144213009</v>
       </c>
       <c r="C5" t="n">
-        <v>161.8656527376929</v>
+        <v>248.0631011705629</v>
       </c>
       <c r="D5" t="n">
-        <v>137.4692222871597</v>
+        <v>143.0651842013665</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.23656980565704</v>
+        <v>35.46170882509904</v>
       </c>
       <c r="C6" t="n">
-        <v>234.9086636813599</v>
+        <v>292.7100415165951</v>
       </c>
       <c r="D6" t="n">
-        <v>69.71586797397451</v>
+        <v>68.06555008313562</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>14.97165248976386</v>
       </c>
       <c r="C7" t="n">
-        <v>231.5815207116674</v>
+        <v>241.8221310146658</v>
       </c>
       <c r="D7" t="n">
-        <v>40.3036885024443</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.923464736797754</v>
       </c>
       <c r="C8" t="n">
-        <v>162.7246819789088</v>
+        <v>166.3964183927919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>72.22030636750809</v>
+        <v>71.22186895228909</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.82929907264807</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.21334235145782</v>
+      </c>
+      <c r="D14" t="n">
         <v>13.82791641431633</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.230530784048753</v>
+        <v>1.275290267816607</v>
       </c>
       <c r="C2" t="n">
-        <v>3.211296740591317</v>
+        <v>1.727875959474386</v>
       </c>
       <c r="D2" t="n">
-        <v>8.069966128908781</v>
+        <v>11.38532812615026</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.72974164389164</v>
+        <v>9.169523557665208</v>
       </c>
       <c r="C3" t="n">
-        <v>19.61531913085127</v>
+        <v>16.02703127182918</v>
       </c>
       <c r="D3" t="n">
-        <v>64.26520471999621</v>
+        <v>76.32597526666828</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>28.88203571123692</v>
       </c>
       <c r="C4" t="n">
-        <v>60.44424265506763</v>
+        <v>85.75271672284615</v>
       </c>
       <c r="D4" t="n">
-        <v>155.5009823710608</v>
+        <v>171.3778062441402</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.16855147662353</v>
+        <v>45.70035563268903</v>
       </c>
       <c r="C5" t="n">
-        <v>154.9688751153591</v>
+        <v>237.7547502759714</v>
       </c>
       <c r="D5" t="n">
-        <v>154.379826492811</v>
+        <v>160.8348176482337</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.84413276586557</v>
+        <v>40.77492740048278</v>
       </c>
       <c r="C6" t="n">
-        <v>254.189206845063</v>
+        <v>336.9868629781262</v>
       </c>
       <c r="D6" t="n">
-        <v>83.68319256229388</v>
+        <v>81.34859652159497</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>13.35471402086936</v>
       </c>
       <c r="C7" t="n">
-        <v>276.2569317411227</v>
+        <v>297.6963381064646</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>204.1986137448153</v>
+        <v>208.0372472684203</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>83.6468678972367</v>
+        <v>77.21249344360311</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.992767913171777</v>
+        <v>1.809361018926871</v>
       </c>
       <c r="C2" t="n">
-        <v>6.859471209572464</v>
+        <v>10.27497147264712</v>
       </c>
       <c r="D2" t="n">
-        <v>15.39380400258999</v>
+        <v>14.04291916154637</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.78449853115121</v>
+        <v>6.940956269024949</v>
       </c>
       <c r="C3" t="n">
-        <v>16.13502351929633</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D3" t="n">
-        <v>57.28006980428015</v>
+        <v>69.38992773616455</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.93232582833176</v>
+        <v>23.63655772744621</v>
       </c>
       <c r="C4" t="n">
-        <v>55.09666291003525</v>
+        <v>66.18746672491146</v>
       </c>
       <c r="D4" t="n">
-        <v>152.4379295338107</v>
+        <v>169.7952289448943</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.33406592801374</v>
+        <v>45.11130701014094</v>
       </c>
       <c r="C5" t="n">
-        <v>135.7511638047277</v>
+        <v>204.8171147984909</v>
       </c>
       <c r="D5" t="n">
-        <v>167.6334205001429</v>
+        <v>175.438314748905</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.18880832551422</v>
+        <v>47.93972214607601</v>
       </c>
       <c r="C6" t="n">
-        <v>251.9753657719864</v>
+        <v>353.5705451982633</v>
       </c>
       <c r="D6" t="n">
-        <v>105.33858342257</v>
+        <v>103.0442390377452</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.21899615797182</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="C7" t="n">
-        <v>317.7583524427481</v>
+        <v>369.3806102274539</v>
       </c>
       <c r="D7" t="n">
-        <v>55.39511421212627</v>
+        <v>52.28101049425539</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>267.8698611037422</v>
+        <v>278.8850703453914</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>146.9921750183536</v>
+        <v>138.4499882437021</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>56.08724634362028</v>
+        <v>50.53546307610457</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
+        <v>18.65909686691488</v>
+      </c>
+      <c r="D12" t="n">
         <v>19.96089432274615</v>
-      </c>
-      <c r="D12" t="n">
-        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.157120690408495</v>
+        <v>5.120796025351362</v>
       </c>
       <c r="C2" t="n">
-        <v>11.46386794249</v>
+        <v>14.76254022875929</v>
       </c>
       <c r="D2" t="n">
-        <v>18.61099122940679</v>
+        <v>12.01462840457247</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.854922323949725</v>
+        <v>1.322414157620454</v>
       </c>
       <c r="C2" t="n">
-        <v>3.896556638155591</v>
+        <v>6.08192702780899</v>
       </c>
       <c r="D2" t="n">
-        <v>11.33035025471244</v>
+        <v>10.44775906859456</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.81457285708437</v>
+        <v>9.660397409788615</v>
       </c>
       <c r="C3" t="n">
-        <v>21.74080291054562</v>
+        <v>21.37264752145306</v>
       </c>
       <c r="D3" t="n">
-        <v>63.85287068421255</v>
+        <v>75.56021205735577</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.85270645329653</v>
+        <v>33.54042856788804</v>
       </c>
       <c r="C4" t="n">
-        <v>79.00123776074084</v>
+        <v>101.042455468786</v>
       </c>
       <c r="D4" t="n">
-        <v>156.1774065392868</v>
+        <v>171.8500268898829</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>27.41530464109218</v>
       </c>
       <c r="C5" t="n">
-        <v>207.5660083703819</v>
+        <v>301.0529335072844</v>
       </c>
       <c r="D5" t="n">
-        <v>153.7662341776567</v>
+        <v>157.7177686872501</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.00507296943726</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>261.1527433112856</v>
+        <v>305.6710747080614</v>
       </c>
       <c r="D6" t="n">
-        <v>83.32092765942681</v>
+        <v>79.77878194250432</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>188.3433883212293</v>
+        <v>196.1286476159065</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>108.3162242095506</v>
+        <v>102.0575825949772</v>
       </c>
       <c r="D8" t="n">
-        <v>24.70077223884975</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>38.49530923122167</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.34948648717864</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>14.9264920953685</v>
+      </c>
+      <c r="D11" t="n">
         <v>15.99267010218054</v>
-      </c>
-      <c r="D11" t="n">
-        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.073091298470769</v>
+        <v>6.529603980945535</v>
       </c>
       <c r="C2" t="n">
-        <v>6.07898178469625</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="D2" t="n">
-        <v>15.34766186049039</v>
+        <v>13.47350549308323</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.9563043793944</v>
+        <v>10.88267330157589</v>
       </c>
       <c r="C3" t="n">
-        <v>28.8879261974624</v>
+        <v>37.19842051391165</v>
       </c>
       <c r="D3" t="n">
-        <v>18.77101610519901</v>
+        <v>13.22905031472577</v>
       </c>
     </row>
     <row r="4">
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4616,7 +4616,7 @@
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39595891609006</v>
+        <v>13.39652872381744</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13178491364795</v>
+        <v>70.13476802469128</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57599516659883</v>
+        <v>1.576062202802051</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.569053815564656</v>
+        <v>4.334416114249668</v>
       </c>
       <c r="C2" t="n">
-        <v>6.17421131200819</v>
+        <v>5.301437602932777</v>
       </c>
       <c r="D2" t="n">
-        <v>16.09771710653495</v>
+        <v>18.51674344979909</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95969159086365</v>
+        <v>17.86289947877071</v>
       </c>
       <c r="C3" t="n">
-        <v>25.64815877344792</v>
+        <v>29.93839624100649</v>
       </c>
       <c r="D3" t="n">
-        <v>27.12568906833937</v>
+        <v>21.34810382884689</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.81377103582937</v>
+        <v>12.72443199474291</v>
       </c>
       <c r="C4" t="n">
-        <v>44.56741878198821</v>
+        <v>57.21527445579986</v>
       </c>
       <c r="D4" t="n">
-        <v>24.91282974296706</v>
+        <v>22.00292954757952</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4896,7 +4896,7 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4910,7 +4910,7 @@
         <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
         <v>36.63391558396972</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43568390063902</v>
+        <v>15.43594335242289</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11486807724927</v>
+        <v>86.11631554509613</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249617663292425</v>
+        <v>3.249672284720608</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.176755644493432</v>
+        <v>4.642684893383167</v>
       </c>
       <c r="C2" t="n">
-        <v>4.899902791895831</v>
+        <v>6.224280444924777</v>
       </c>
       <c r="D2" t="n">
-        <v>17.26501512688441</v>
+        <v>32.77172011546278</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.32155558310322</v>
+        <v>16.4050041379642</v>
       </c>
       <c r="C3" t="n">
-        <v>24.66150233067988</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D3" t="n">
-        <v>33.70830742531424</v>
+        <v>31.20485077948487</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.18535469412017</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="C4" t="n">
-        <v>55.51783267515713</v>
+        <v>67.50202690089795</v>
       </c>
       <c r="D4" t="n">
-        <v>32.9022925601276</v>
+        <v>27.75891633757857</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.388273369263</v>
+        <v>11.33918598405066</v>
       </c>
       <c r="C5" t="n">
-        <v>49.2837347531899</v>
+        <v>61.53103736366885</v>
       </c>
       <c r="D5" t="n">
-        <v>31.58773238414113</v>
+        <v>30.58144098728815</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.31700669748049</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
         <v>36.54850353370026</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72446280722005</v>
+        <v>16.72270653728977</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0192231240423</v>
+        <v>102.0085098774676</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181115701805013</v>
+        <v>4.180676634322442</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.944883259841937</v>
+        <v>4.760494617892784</v>
       </c>
       <c r="C2" t="n">
-        <v>7.802930753353649</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D2" t="n">
-        <v>25.31829154482099</v>
+        <v>31.99908467222054</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.03332266868216</v>
+        <v>16.08593613408399</v>
       </c>
       <c r="C3" t="n">
-        <v>21.62790192455724</v>
+        <v>24.21971586376881</v>
       </c>
       <c r="D3" t="n">
-        <v>39.32881303212722</v>
+        <v>49.1708337672015</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.9631198600619</v>
+        <v>28.51191682673587</v>
       </c>
       <c r="C4" t="n">
-        <v>58.36391926976863</v>
+        <v>63.90293981712914</v>
       </c>
       <c r="D4" t="n">
-        <v>41.8744848292392</v>
+        <v>36.64176956560371</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.80738182798515</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="C5" t="n">
-        <v>78.04894248762143</v>
+        <v>94.39504176333082</v>
       </c>
       <c r="D5" t="n">
-        <v>35.78470381979624</v>
+        <v>33.57577148524092</v>
       </c>
     </row>
     <row r="6">
@@ -5504,10 +5504,10 @@
         <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>46.249152599363</v>
+        <v>56.35231822376692</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.73257338047992</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04396042240602</v>
+        <v>18.03569781165819</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7153608509345</v>
+        <v>117.6614571522463</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014653474135338</v>
+        <v>6.011899270552731</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.308129910413257</v>
+        <v>5.235660506748239</v>
       </c>
       <c r="C2" t="n">
-        <v>5.175773896789184</v>
+        <v>9.097855975255191</v>
       </c>
       <c r="D2" t="n">
-        <v>31.17932533917445</v>
+        <v>39.78238047148925</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67284133477433</v>
+        <v>14.34824269756713</v>
       </c>
       <c r="C3" t="n">
-        <v>24.86766934857171</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="D3" t="n">
-        <v>46.86863540074273</v>
+        <v>58.01638058246527</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.10503130882118</v>
+        <v>21.55623434214721</v>
       </c>
       <c r="C4" t="n">
-        <v>46.3541996037174</v>
+        <v>51.31889774409352</v>
       </c>
       <c r="D4" t="n">
-        <v>45.0013512672653</v>
+        <v>44.4015034199705</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.02765316663493</v>
+        <v>20.39580855572749</v>
       </c>
       <c r="C5" t="n">
-        <v>69.85134915716057</v>
+        <v>79.30067081053612</v>
       </c>
       <c r="D5" t="n">
-        <v>34.06664533736433</v>
+        <v>31.51410130632262</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.67298020349458</v>
+        <v>11.47172192412398</v>
       </c>
       <c r="C6" t="n">
-        <v>58.04288777047993</v>
+        <v>69.6756163181004</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>28.44613973055133</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.63281066307846</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049214935816845</v>
+        <v>7.043328061944512</v>
       </c>
       <c r="C21" t="n">
-        <v>66.96754189026002</v>
+        <v>66.0312005807298</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405759334885528</v>
+        <v>4.40208003871532</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.165956419746716</v>
+        <v>4.374667770123787</v>
       </c>
       <c r="C2" t="n">
-        <v>8.072911372021522</v>
+        <v>9.785079368227958</v>
       </c>
       <c r="D2" t="n">
-        <v>30.59616720285184</v>
+        <v>37.13067992231861</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.83545160078081</v>
+        <v>16.67007601811084</v>
       </c>
       <c r="C3" t="n">
-        <v>21.87333885061894</v>
+        <v>30.11020208924968</v>
       </c>
       <c r="D3" t="n">
-        <v>61.73229564303944</v>
+        <v>77.41571521838223</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.92407093607028</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="C4" t="n">
-        <v>56.44951124648735</v>
+        <v>51.72730478906019</v>
       </c>
       <c r="D4" t="n">
-        <v>58.68298727364885</v>
+        <v>64.50278766442393</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.53802310412304</v>
+        <v>27.43984833369836</v>
       </c>
       <c r="C5" t="n">
-        <v>79.69336989223484</v>
+        <v>88.79907984912401</v>
       </c>
       <c r="D5" t="n">
-        <v>43.58959806855839</v>
+        <v>40.59526757060561</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.56859615167493</v>
+        <v>20.44784118405257</v>
       </c>
       <c r="C6" t="n">
-        <v>89.31842438467058</v>
+        <v>102.4404641996334</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>60.7250224984822</v>
+        <v>71.56449890107125</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -6154,10 +6154,10 @@
         <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>29.95803119509142</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,7 +6221,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
         <v>20.81305133003238</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.268159484288485</v>
+        <v>7.258981029111088</v>
       </c>
       <c r="C21" t="n">
-        <v>76.3156745850291</v>
+        <v>75.31192817702754</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451119613216364</v>
+        <v>5.444235771833316</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.568072067860409</v>
+        <v>3.916191592240526</v>
       </c>
       <c r="C2" t="n">
-        <v>6.416702994957152</v>
+        <v>12.52611895848505</v>
       </c>
       <c r="D2" t="n">
-        <v>29.78131660832699</v>
+        <v>28.06816686441631</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.03256190515617</v>
+        <v>15.92394776288327</v>
       </c>
       <c r="C3" t="n">
-        <v>27.5478405811655</v>
+        <v>34.73914251477338</v>
       </c>
       <c r="D3" t="n">
-        <v>71.88356690495145</v>
+        <v>88.41619824446775</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.23710958500477</v>
+        <v>29.02242563294421</v>
       </c>
       <c r="C4" t="n">
-        <v>55.50506995500192</v>
+        <v>65.17921183264998</v>
       </c>
       <c r="D4" t="n">
-        <v>76.43593100954392</v>
+        <v>86.86307337634929</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.79728661350221</v>
+        <v>33.33033455917922</v>
       </c>
       <c r="C5" t="n">
-        <v>93.53601252211487</v>
+        <v>91.71977926925827</v>
       </c>
       <c r="D5" t="n">
-        <v>54.87969666739671</v>
+        <v>54.5606286635165</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.38370878810704</v>
+        <v>29.06169554111408</v>
       </c>
       <c r="C6" t="n">
-        <v>108.8807291394925</v>
+        <v>123.6530868452943</v>
       </c>
       <c r="D6" t="n">
-        <v>41.33845058272045</v>
+        <v>38.96360288614742</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.84620976779852</v>
+        <v>17.42700349808513</v>
       </c>
       <c r="C7" t="n">
-        <v>98.15415372289186</v>
+        <v>112.7065999429423</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>36.23139902522853</v>
       </c>
     </row>
     <row r="8">
@@ -6465,10 +6465,10 @@
         <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>57.24570863463151</v>
+        <v>65.42366701100744</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
         <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6510,7 +6510,7 @@
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473735536618086</v>
+        <v>7.460453093356549</v>
       </c>
       <c r="C21" t="n">
-        <v>85.01374172903073</v>
+        <v>83.93009730026118</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539518594540825</v>
+        <v>6.527896456686981</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641835961</v>
+        <v>10.84497633679118</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890722420782</v>
+        <v>37.78907195785489</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.522330836388309</v>
+        <v>6.696501090667494</v>
       </c>
       <c r="C2" t="n">
-        <v>9.669233139126835</v>
+        <v>6.346998907955629</v>
       </c>
       <c r="D2" t="n">
-        <v>26.00355144238527</v>
+        <v>21.18513370994192</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48568737616169</v>
+        <v>16.61117115585603</v>
       </c>
       <c r="C3" t="n">
-        <v>42.05807164993336</v>
+        <v>35.38709599957628</v>
       </c>
       <c r="D3" t="n">
-        <v>89.81027998449821</v>
+        <v>57.1868037723767</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.85200244303276</v>
+        <v>35.79943003535994</v>
       </c>
       <c r="C4" t="n">
-        <v>75.74674412116265</v>
+        <v>91.27897455005143</v>
       </c>
       <c r="D4" t="n">
-        <v>108.9298165247048</v>
+        <v>85.66337768175968</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.14089830998859</v>
+        <v>45.60218086226435</v>
       </c>
       <c r="C5" t="n">
-        <v>106.2741889847172</v>
+        <v>156.981457909065</v>
       </c>
       <c r="D5" t="n">
-        <v>70.73492209098271</v>
+        <v>62.58641614573418</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.07177506006381</v>
+        <v>45.08185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>133.7562524696982</v>
+        <v>167.6883983715807</v>
       </c>
       <c r="D6" t="n">
-        <v>46.65166915810419</v>
+        <v>43.79380159104173</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>32.87774886752143</v>
       </c>
       <c r="C7" t="n">
-        <v>146.1832149100543</v>
+        <v>135.4635117273834</v>
       </c>
       <c r="D7" t="n">
-        <v>38.86640986342697</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>17.27385085622263</v>
       </c>
       <c r="C8" t="n">
-        <v>106.647253112331</v>
+        <v>89.20650514638642</v>
       </c>
       <c r="D8" t="n">
         <v>35.71598148049896</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -996,7 +996,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.646736221778488</v>
+        <v>7.649775819534706</v>
       </c>
       <c r="C21" t="n">
-        <v>92.71667668906416</v>
+        <v>92.75353181185831</v>
       </c>
       <c r="D21" t="n">
-        <v>7.646736221778488</v>
+        <v>7.649775819534706</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.850234569606743</v>
+        <v>7.237444075707486</v>
       </c>
       <c r="C2" t="n">
-        <v>14.59269787592459</v>
+        <v>6.225262192629025</v>
       </c>
       <c r="D2" t="n">
-        <v>31.23921194913351</v>
+        <v>25.77284073188726</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.23810702824224</v>
+        <v>19.07535789351553</v>
       </c>
       <c r="C3" t="n">
-        <v>39.55952374262523</v>
+        <v>29.93348750248525</v>
       </c>
       <c r="D3" t="n">
-        <v>89.06415172927063</v>
+        <v>59.67062546412114</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.60125586782233</v>
+        <v>33.25964872447344</v>
       </c>
       <c r="C4" t="n">
-        <v>89.64534637018475</v>
+        <v>88.82853228025141</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6962837442811</v>
+        <v>91.90434783765667</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>48.81740459367266</v>
       </c>
       <c r="C5" t="n">
-        <v>120.4358996184775</v>
+        <v>161.8901964302991</v>
       </c>
       <c r="D5" t="n">
-        <v>89.8790023237955</v>
+        <v>76.35542769779569</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.27053006467818</v>
+        <v>52.20639766873265</v>
       </c>
       <c r="C6" t="n">
-        <v>149.9776697869682</v>
+        <v>202.3853257350715</v>
       </c>
       <c r="D6" t="n">
-        <v>55.54728510628455</v>
+        <v>51.24035792775378</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>42.33983324105218</v>
       </c>
       <c r="C7" t="n">
-        <v>166.9039819558875</v>
+        <v>182.1151808854876</v>
       </c>
       <c r="D7" t="n">
-        <v>42.93869934064274</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.77730750205199</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>146.5356623358789</v>
+        <v>130.0962970282661</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>11.98124898262807</v>
       </c>
       <c r="C9" t="n">
-        <v>88.74999246391164</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
         <v>34.71459882216721</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.816791094585173</v>
+        <v>7.818314461441287</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6411853427841</v>
+        <v>100.6607986910566</v>
       </c>
       <c r="D21" t="n">
-        <v>8.79388998140832</v>
+        <v>8.795603769121447</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.066219064541041</v>
+        <v>9.660397409788613</v>
       </c>
       <c r="C2" t="n">
-        <v>12.12556589515235</v>
+        <v>7.880488821989147</v>
       </c>
       <c r="D2" t="n">
-        <v>28.68863141350029</v>
+        <v>24.95799013736241</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.27385085622263</v>
+        <v>20.82286880707485</v>
       </c>
       <c r="C3" t="n">
-        <v>46.74591693771188</v>
+        <v>27.0864191601695</v>
       </c>
       <c r="D3" t="n">
-        <v>91.41543748094176</v>
+        <v>64.15230373400782</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.77993394999525</v>
+        <v>33.91054745238907</v>
       </c>
       <c r="C4" t="n">
-        <v>92.36380576324416</v>
+        <v>82.43440948249193</v>
       </c>
       <c r="D4" t="n">
-        <v>135.4635117273834</v>
+        <v>98.20913159432968</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.62610266006477</v>
+        <v>48.74377351585415</v>
       </c>
       <c r="C5" t="n">
-        <v>138.8682127657113</v>
+        <v>160.4666622591412</v>
       </c>
       <c r="D5" t="n">
-        <v>106.1514705216864</v>
+        <v>86.78649705541805</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.53720558733482</v>
+        <v>57.19760299712343</v>
       </c>
       <c r="C6" t="n">
-        <v>165.4745572985042</v>
+        <v>222.9136702308723</v>
       </c>
       <c r="D6" t="n">
-        <v>67.13976199803088</v>
+        <v>60.49823877880121</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.48334833232147</v>
+        <v>49.94543270585223</v>
       </c>
       <c r="C7" t="n">
-        <v>186.6665632423758</v>
+        <v>225.7126329356799</v>
       </c>
       <c r="D7" t="n">
-        <v>47.13076203777662</v>
+        <v>45.33416373900496</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.20284622634736</v>
+        <v>33.04562772494764</v>
       </c>
       <c r="C8" t="n">
-        <v>177.0778334149972</v>
+        <v>176.0764507566654</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7562488319063</v>
+        <v>17.08437354930299</v>
       </c>
       <c r="C9" t="n">
-        <v>127.1343642045534</v>
+        <v>108.6078032777119</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>69.46846755250431</v>
+        <v>60.64255569132548</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.40324593120072</v>
+        <v>39.27088991757665</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -1559,10 +1559,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1576,7 +1576,7 @@
         <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1618,7 +1618,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.969808759854629</v>
+        <v>7.970306710528112</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5924182580375</v>
+        <v>107.5991405921295</v>
       </c>
       <c r="D21" t="n">
-        <v>9.962260949818287</v>
+        <v>9.96288338816014</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.682355712180538</v>
+        <v>8.728718838458391</v>
       </c>
       <c r="C2" t="n">
-        <v>8.536296288426016</v>
+        <v>5.547856276698725</v>
       </c>
       <c r="D2" t="n">
-        <v>23.82799852977434</v>
+        <v>20.58135887183013</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0227444281137</v>
+        <v>23.88101290580366</v>
       </c>
       <c r="C3" t="n">
-        <v>66.04216806468294</v>
+        <v>43.48160582109124</v>
       </c>
       <c r="D3" t="n">
-        <v>99.37250262386215</v>
+        <v>70.46985021083604</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.99918248321178</v>
+        <v>23.41959148480766</v>
       </c>
       <c r="C4" t="n">
-        <v>118.0806868759894</v>
+        <v>123.6197074233499</v>
       </c>
       <c r="D4" t="n">
-        <v>127.1039300257218</v>
+        <v>94.78872259273379</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.77716863333176</v>
+        <v>32.22586839190156</v>
       </c>
       <c r="C5" t="n">
-        <v>98.86199381765383</v>
+        <v>133.198619773686</v>
       </c>
       <c r="D5" t="n">
-        <v>67.61787312999908</v>
+        <v>58.63488163614076</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.1170332654504</v>
+        <v>30.99377502307181</v>
       </c>
       <c r="C6" t="n">
-        <v>122.9285570395601</v>
+        <v>148.6493651431223</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>29.82647700272235</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>124.5042621048762</v>
+        <v>123.7856227853676</v>
       </c>
       <c r="D7" t="n">
-        <v>28.02693346083794</v>
+        <v>27.84727363096077</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C8" t="n">
-        <v>93.71272710887928</v>
+        <v>80.02716411167874</v>
       </c>
       <c r="D8" t="n">
-        <v>26.45319189093031</v>
+        <v>26.62008900065226</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>53.0281204971872</v>
+        <v>46.26093357181394</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
         <v>28.32833000604172</v>
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>27.8983245115816</v>
@@ -1856,10 +1856,10 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1873,7 +1873,7 @@
         <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1915,7 +1915,7 @@
         <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.37631247036279</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.563744166415922</v>
+        <v>5.14926670877452</v>
       </c>
       <c r="C2" t="n">
-        <v>5.048146695237099</v>
+        <v>2.728276870101886</v>
       </c>
       <c r="D2" t="n">
-        <v>16.83010089390307</v>
+        <v>14.53968349989526</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.23382018452676</v>
+        <v>27.24840753137022</v>
       </c>
       <c r="C3" t="n">
-        <v>50.96252332745193</v>
+        <v>33.21743357319083</v>
       </c>
       <c r="D3" t="n">
-        <v>96.33399347921828</v>
+        <v>71.49577656177397</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.31222113214627</v>
+        <v>32.62151271671301</v>
       </c>
       <c r="C4" t="n">
-        <v>142.6999740553866</v>
+        <v>121.0161125116873</v>
       </c>
       <c r="D4" t="n">
-        <v>144.5760939182023</v>
+        <v>106.4538488145944</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.30516897176729</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>151.9990883100124</v>
+        <v>177.9417713947344</v>
       </c>
       <c r="D5" t="n">
-        <v>87.22828352232911</v>
+        <v>72.20754364735292</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.46421209985528</v>
+        <v>36.22649028670731</v>
       </c>
       <c r="C6" t="n">
-        <v>143.2556432559903</v>
+        <v>179.0796169839565</v>
       </c>
       <c r="D6" t="n">
-        <v>38.44033135978387</v>
+        <v>36.06548366321083</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.10949807898591</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>148.5187926984575</v>
+        <v>159.4181557110055</v>
       </c>
       <c r="D7" t="n">
-        <v>30.60205768907732</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>119.9155733352267</v>
+        <v>105.2286276796944</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>55.91249525226433</v>
+        <v>50.36562072326985</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>34.02246669067321</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
         <v>29.18245050873644</v>
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2212,7 +2212,7 @@
         <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.855904071653971</v>
+        <v>4.899902791895831</v>
       </c>
       <c r="C2" t="n">
-        <v>4.51211244871834</v>
+        <v>6.746570223584081</v>
       </c>
       <c r="D2" t="n">
-        <v>20.73352976598839</v>
+        <v>13.50393967191488</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35591675275186</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8422260237193</v>
+        <v>21.71625921793945</v>
       </c>
       <c r="D3" t="n">
-        <v>89.12796533004668</v>
+        <v>66.85210992068656</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.13652935081509</v>
+        <v>41.64475586644545</v>
       </c>
       <c r="C4" t="n">
-        <v>134.9274774808646</v>
+        <v>102.1911002827547</v>
       </c>
       <c r="D4" t="n">
-        <v>155.0542871656285</v>
+        <v>116.1790415728633</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.41025703385071</v>
+        <v>41.35612204139689</v>
       </c>
       <c r="C5" t="n">
-        <v>205.5288818840698</v>
+        <v>198.9511722656162</v>
       </c>
       <c r="D5" t="n">
-        <v>113.88273369263</v>
+        <v>90.34533248331273</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.85164259013428</v>
+        <v>41.29819892684633</v>
       </c>
       <c r="C6" t="n">
-        <v>186.687179944165</v>
+        <v>227.8243722475149</v>
       </c>
       <c r="D6" t="n">
-        <v>52.97117913034091</v>
+        <v>47.41645061971246</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.41566449399068</v>
+        <v>29.10489244010094</v>
       </c>
       <c r="C7" t="n">
-        <v>176.4858395493364</v>
+        <v>203.3749274209522</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>13.93590866178347</v>
       </c>
       <c r="C8" t="n">
-        <v>154.2963779379499</v>
+        <v>152.0432669567035</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>92.85467961536754</v>
+        <v>83.20311793491715</v>
       </c>
       <c r="D9" t="n">
         <v>28.95468504135117</v>
@@ -2450,10 +2450,10 @@
         <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>15.0501923061036</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.38885420633975</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.731802950291373</v>
+        <v>2.975677291572082</v>
       </c>
       <c r="C2" t="n">
-        <v>2.240348261091221</v>
+        <v>3.257438882690916</v>
       </c>
       <c r="D2" t="n">
-        <v>14.618223316235</v>
+        <v>9.419869222248145</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4821612959722</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="C3" t="n">
-        <v>29.78131660832699</v>
+        <v>24.97075285751762</v>
       </c>
       <c r="D3" t="n">
-        <v>88.66654390905069</v>
+        <v>65.42366701100745</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>45.79263991688822</v>
       </c>
       <c r="C4" t="n">
-        <v>132.745052334324</v>
+        <v>95.82250292530568</v>
       </c>
       <c r="D4" t="n">
-        <v>164.8050053642078</v>
+        <v>123.6452328636603</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.85833489761475</v>
+        <v>43.04963683122264</v>
       </c>
       <c r="C5" t="n">
-        <v>247.6213147036518</v>
+        <v>230.6125357275758</v>
       </c>
       <c r="D5" t="n">
-        <v>116.6561709571273</v>
+        <v>95.40133316018381</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.65288758551991</v>
+        <v>34.45541742824607</v>
       </c>
       <c r="C6" t="n">
-        <v>218.6872463640898</v>
+        <v>265.7011804250611</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.425939634922873</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>189.4213473004923</v>
+        <v>206.369257918905</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>112.2383062880166</v>
+        <v>105.9796646734432</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>33.28124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>12.59876828859932</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>8.679631453246051</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.829977720716055</v>
+        <v>3.645229225868407</v>
       </c>
       <c r="C2" t="n">
-        <v>2.87161203492192</v>
+        <v>5.17086515826795</v>
       </c>
       <c r="D2" t="n">
-        <v>15.71974424039993</v>
+        <v>8.483281912396688</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.01030050312798</v>
+        <v>16.41482161500667</v>
       </c>
       <c r="C3" t="n">
-        <v>19.45333075965055</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="D3" t="n">
-        <v>80.85183218324607</v>
+        <v>58.78214379177777</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.36625831360885</v>
+        <v>43.92928277422778</v>
       </c>
       <c r="C4" t="n">
-        <v>106.3006961727319</v>
+        <v>80.50723873905544</v>
       </c>
       <c r="D4" t="n">
-        <v>169.8845679859808</v>
+        <v>127.0145909846353</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.68148144213009</v>
+        <v>53.70159942230054</v>
       </c>
       <c r="C5" t="n">
-        <v>248.0631011705629</v>
+        <v>205.7743188101315</v>
       </c>
       <c r="D5" t="n">
-        <v>143.0651842013665</v>
+        <v>112.9991607588079</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.46170882509904</v>
+        <v>43.75354993516761</v>
       </c>
       <c r="C6" t="n">
-        <v>292.7100415165951</v>
+        <v>314.9289555591089</v>
       </c>
       <c r="D6" t="n">
-        <v>68.06555008313562</v>
+        <v>61.34352355215771</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>19.10382857693868</v>
       </c>
       <c r="C7" t="n">
-        <v>241.8221310146658</v>
+        <v>280.5088810482156</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>166.3964183927919</v>
+        <v>172.0709201233385</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>67.8937442348924</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3131,7 +3131,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.275290267816607</v>
+        <v>2.514255870576081</v>
       </c>
       <c r="C2" t="n">
-        <v>1.727875959474386</v>
+        <v>3.292781800043802</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38532812615026</v>
+        <v>6.32834570157494</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.169523557665208</v>
+        <v>14.88329519638165</v>
       </c>
       <c r="C3" t="n">
-        <v>16.02703127182918</v>
+        <v>19.56623174563893</v>
       </c>
       <c r="D3" t="n">
-        <v>76.32597526666828</v>
+        <v>53.84395283941632</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.88203571123692</v>
+        <v>40.10046672766521</v>
       </c>
       <c r="C4" t="n">
-        <v>85.75271672284615</v>
+        <v>68.75277347610837</v>
       </c>
       <c r="D4" t="n">
-        <v>171.3778062441402</v>
+        <v>127.5889133916197</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.70035563268903</v>
+        <v>58.75760009917161</v>
       </c>
       <c r="C5" t="n">
-        <v>237.7547502759714</v>
+        <v>189.7963749235146</v>
       </c>
       <c r="D5" t="n">
-        <v>160.8348176482337</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.77492740048278</v>
+        <v>51.24035792775378</v>
       </c>
       <c r="C6" t="n">
-        <v>336.9868629781262</v>
+        <v>334.9742801844203</v>
       </c>
       <c r="D6" t="n">
-        <v>81.34859652159497</v>
+        <v>71.32593420893927</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.35471402086936</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>297.6963381064646</v>
+        <v>343.8090277749372</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>41.20198765183014</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>208.0372472684203</v>
+        <v>222.3069501496477</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>77.21249344360311</v>
+        <v>76.87968097186344</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>10.926851948267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.809361018926871</v>
+        <v>3.259402378099411</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27497147264712</v>
+        <v>11.19192382841364</v>
       </c>
       <c r="D2" t="n">
-        <v>14.04291916154637</v>
+        <v>12.42205370183489</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.940956269024949</v>
+        <v>11.85951226730147</v>
       </c>
       <c r="C3" t="n">
-        <v>11.82515109765283</v>
+        <v>16.36573422979433</v>
       </c>
       <c r="D3" t="n">
-        <v>69.38992773616455</v>
+        <v>48.2479909252095</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.63655772744621</v>
+        <v>34.42105625859742</v>
       </c>
       <c r="C4" t="n">
-        <v>66.18746672491146</v>
+        <v>59.93373384885928</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7952289448943</v>
+        <v>124.1429789497134</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.11130701014094</v>
+        <v>59.66571672559991</v>
       </c>
       <c r="C5" t="n">
-        <v>204.8171147984909</v>
+        <v>163.1664684458199</v>
       </c>
       <c r="D5" t="n">
-        <v>175.438314748905</v>
+        <v>137.8619213688584</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.93972214607601</v>
+        <v>61.26302024040947</v>
       </c>
       <c r="C6" t="n">
-        <v>353.5705451982633</v>
+        <v>323.3415516367998</v>
       </c>
       <c r="D6" t="n">
-        <v>103.0442390377452</v>
+        <v>87.18508662334226</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.07441720354028</v>
+        <v>30.96137734883166</v>
       </c>
       <c r="C7" t="n">
-        <v>369.3806102274539</v>
+        <v>399.683234866736</v>
       </c>
       <c r="D7" t="n">
-        <v>52.28101049425539</v>
+        <v>48.38838084691679</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>278.8850703453914</v>
+        <v>312.4313893995049</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>138.4499882437021</v>
+        <v>146.1046750937145</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>50.53546307610457</v>
+        <v>50.67781649322036</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.36962016288231</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.120796025351362</v>
+        <v>7.65468685001238</v>
       </c>
       <c r="C2" t="n">
-        <v>14.76254022875929</v>
+        <v>10.89838126484384</v>
       </c>
       <c r="D2" t="n">
-        <v>12.01462840457247</v>
+        <v>9.447358157967058</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.322414157620454</v>
+        <v>2.358157985600839</v>
       </c>
       <c r="C2" t="n">
-        <v>6.08192702780899</v>
+        <v>6.535494467171016</v>
       </c>
       <c r="D2" t="n">
-        <v>10.44775906859456</v>
+        <v>9.241191140075227</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.660397409788615</v>
+        <v>15.80613803837365</v>
       </c>
       <c r="C3" t="n">
-        <v>21.37264752145306</v>
+        <v>26.37956081311179</v>
       </c>
       <c r="D3" t="n">
-        <v>75.56021205735577</v>
+        <v>53.00455855228529</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.54042856788804</v>
+        <v>45.98408071921636</v>
       </c>
       <c r="C4" t="n">
-        <v>101.042455468786</v>
+        <v>88.90510860118265</v>
       </c>
       <c r="D4" t="n">
-        <v>171.8500268898829</v>
+        <v>128.035608597052</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.41530464109218</v>
+        <v>35.61289797155305</v>
       </c>
       <c r="C5" t="n">
-        <v>301.0529335072844</v>
+        <v>259.8686173141307</v>
       </c>
       <c r="D5" t="n">
-        <v>157.7177686872501</v>
+        <v>125.8109682992288</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93336432929824</v>
+        <v>19.20003985195487</v>
       </c>
       <c r="C6" t="n">
-        <v>305.6710747080614</v>
+        <v>323.4623066044222</v>
       </c>
       <c r="D6" t="n">
-        <v>79.77878194250432</v>
+        <v>69.59511300635215</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.491495746929157</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>196.1286476159065</v>
+        <v>219.7239719397744</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>102.0575825949772</v>
+        <v>107.6486357706628</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>23.86628669023996</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.49530923122167</v>
+        <v>38.60624672180155</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>15.28188476430585</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.365873098514571</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.105709956889166</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.529603980945535</v>
+        <v>8.031677968443155</v>
       </c>
       <c r="C2" t="n">
-        <v>6.563965150594174</v>
+        <v>6.184028789050658</v>
       </c>
       <c r="D2" t="n">
-        <v>13.47350549308323</v>
+        <v>8.709083884373454</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.88267330157589</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="C3" t="n">
-        <v>37.19842051391165</v>
+        <v>27.45948328778329</v>
       </c>
       <c r="D3" t="n">
-        <v>13.22905031472577</v>
+        <v>11.06920536538279</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39652872381744</v>
+        <v>13.39719586868497</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13476802469128</v>
+        <v>70.1382607242919</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576062202802051</v>
+        <v>1.576140690433526</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.334416114249668</v>
+        <v>5.14337622254904</v>
       </c>
       <c r="C2" t="n">
-        <v>5.301437602932777</v>
+        <v>7.058765993534567</v>
       </c>
       <c r="D2" t="n">
-        <v>18.51674344979909</v>
+        <v>17.74410800655685</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.86289947877071</v>
+        <v>23.16924582022473</v>
       </c>
       <c r="C3" t="n">
-        <v>29.93839624100649</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D3" t="n">
-        <v>21.34810382884689</v>
+        <v>15.70796326794897</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.72443199474291</v>
+        <v>18.79948678862217</v>
       </c>
       <c r="C4" t="n">
-        <v>57.21527445579986</v>
+        <v>42.38499363544754</v>
       </c>
       <c r="D4" t="n">
-        <v>22.00292954757952</v>
+        <v>20.86704745376596</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.3139636433765</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43594335242289</v>
+        <v>15.43855983339176</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11631554509613</v>
+        <v>86.13091275471191</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249672284720608</v>
+        <v>3.250223122819317</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.642684893383167</v>
+        <v>4.486587008407923</v>
       </c>
       <c r="C2" t="n">
-        <v>6.224280444924777</v>
+        <v>10.6038569535698</v>
       </c>
       <c r="D2" t="n">
-        <v>32.77172011546278</v>
+        <v>30.28397143290136</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.4050041379642</v>
+        <v>20.14546289114455</v>
       </c>
       <c r="C3" t="n">
-        <v>24.36697801940583</v>
+        <v>26.60045404656733</v>
       </c>
       <c r="D3" t="n">
-        <v>31.20485077948487</v>
+        <v>26.25684235008094</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.73415166079414</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="C4" t="n">
-        <v>67.50202690089795</v>
+        <v>54.21603521932585</v>
       </c>
       <c r="D4" t="n">
-        <v>27.75891633757857</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.33918598405066</v>
+        <v>16.00248757922301</v>
       </c>
       <c r="C5" t="n">
-        <v>61.53103736366885</v>
+        <v>46.92754026299754</v>
       </c>
       <c r="D5" t="n">
-        <v>30.58144098728815</v>
+        <v>30.16419821298325</v>
       </c>
     </row>
     <row r="6">
@@ -5190,7 +5190,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
         <v>12.27675504160637</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.15780900513902</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72270653728977</v>
+        <v>16.72794459720835</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0085098774676</v>
+        <v>102.040462042971</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180676634322442</v>
+        <v>4.181986149302088</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.760494617892784</v>
+        <v>5.596943661911066</v>
       </c>
       <c r="C2" t="n">
-        <v>5.154175447295755</v>
+        <v>13.47645073619597</v>
       </c>
       <c r="D2" t="n">
-        <v>31.99908467222054</v>
+        <v>30.44988679491907</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.08593613408399</v>
+        <v>17.51928778228433</v>
       </c>
       <c r="C3" t="n">
-        <v>24.21971586376881</v>
+        <v>34.81768233111313</v>
       </c>
       <c r="D3" t="n">
-        <v>49.1708337672015</v>
+        <v>43.43251843587889</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.51191682673587</v>
+        <v>36.56519324467246</v>
       </c>
       <c r="C4" t="n">
-        <v>63.90293981712914</v>
+        <v>60.96751418143117</v>
       </c>
       <c r="D4" t="n">
-        <v>36.64176956560371</v>
+        <v>31.38352886165779</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.78283813537898</v>
+        <v>32.66765485881262</v>
       </c>
       <c r="C5" t="n">
-        <v>94.39504176333082</v>
+        <v>74.66191290796993</v>
       </c>
       <c r="D5" t="n">
-        <v>33.57577148524092</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.58618549489336</v>
+        <v>13.6050596854523</v>
       </c>
       <c r="C6" t="n">
-        <v>56.35231822376692</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
         <v>39.88448223273092</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5546,7 +5546,7 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
         <v>42.15624642035802</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.73257338047992</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5686,7 +5686,7 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>25.27607639353838</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03569781165819</v>
+        <v>18.04424074620395</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6614571522463</v>
+        <v>117.7171896299972</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011899270552731</v>
+        <v>6.014746915401315</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.235660506748239</v>
+        <v>6.735770998837365</v>
       </c>
       <c r="C2" t="n">
-        <v>9.097855975255191</v>
+        <v>11.05546089752333</v>
       </c>
       <c r="D2" t="n">
-        <v>39.78238047148925</v>
+        <v>23.20851572839459</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.34824269756713</v>
+        <v>16.32155558310322</v>
       </c>
       <c r="C3" t="n">
-        <v>20.69524160552276</v>
+        <v>41.91571823281757</v>
       </c>
       <c r="D3" t="n">
-        <v>58.01638058246527</v>
+        <v>53.5396110510998</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.55623434214721</v>
+        <v>25.24466046700248</v>
       </c>
       <c r="C4" t="n">
-        <v>51.31889774409352</v>
+        <v>62.97126124579891</v>
       </c>
       <c r="D4" t="n">
-        <v>44.4015034199705</v>
+        <v>39.55166976099125</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.39580855572749</v>
+        <v>26.85079971115027</v>
       </c>
       <c r="C5" t="n">
-        <v>79.30067081053612</v>
+        <v>69.72863069412972</v>
       </c>
       <c r="D5" t="n">
-        <v>31.51410130632262</v>
+        <v>28.91246989006857</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.47172192412398</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>69.6756163181004</v>
+        <v>55.8692983532775</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>30.47050349670826</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.168320825782709</v>
       </c>
       <c r="C7" t="n">
-        <v>32.63820242768521</v>
+        <v>27.18852092141116</v>
       </c>
       <c r="D7" t="n">
-        <v>31.20092378866788</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
         <v>18.44213062427633</v>
@@ -5854,10 +5854,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>30.17499743772996</v>
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
         <v>21.06830573313655</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5902,7 +5902,7 @@
         <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.043328061944512</v>
+        <v>7.047066446881602</v>
       </c>
       <c r="C21" t="n">
-        <v>66.0312005807298</v>
+        <v>66.06624793951502</v>
       </c>
       <c r="D21" t="n">
-        <v>4.40208003871532</v>
+        <v>4.404416529301002</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.374667770123787</v>
+        <v>5.310273332270997</v>
       </c>
       <c r="C2" t="n">
-        <v>9.785079368227958</v>
+        <v>7.023423076181681</v>
       </c>
       <c r="D2" t="n">
-        <v>37.13067992231861</v>
+        <v>16.90765896253857</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.67007601811084</v>
+        <v>20.82286880707485</v>
       </c>
       <c r="C3" t="n">
-        <v>30.11020208924968</v>
+        <v>42.70602513473625</v>
       </c>
       <c r="D3" t="n">
-        <v>77.41571521838223</v>
+        <v>60.09768571546849</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.38505038870978</v>
+        <v>29.18834099496192</v>
       </c>
       <c r="C4" t="n">
-        <v>51.72730478906019</v>
+        <v>89.04549852288996</v>
       </c>
       <c r="D4" t="n">
-        <v>64.50278766442393</v>
+        <v>58.42773287054467</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.43984833369836</v>
+        <v>33.57577148524092</v>
       </c>
       <c r="C5" t="n">
-        <v>88.79907984912401</v>
+        <v>97.85570242080085</v>
       </c>
       <c r="D5" t="n">
-        <v>40.59526757060561</v>
+        <v>36.79099521664922</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.44784118405257</v>
+        <v>27.08936440328224</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4404641996334</v>
+        <v>87.74860980557993</v>
       </c>
       <c r="D6" t="n">
-        <v>34.21390749300134</v>
+        <v>33.2881194078966</v>
       </c>
     </row>
     <row r="7">
@@ -6137,10 +6137,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.06095047312131</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>71.56449890107125</v>
+        <v>57.85046522044755</v>
       </c>
       <c r="D7" t="n">
         <v>33.53650157707104</v>
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>32.54493639578176</v>
+        <v>28.53940576245478</v>
       </c>
       <c r="D8" t="n">
         <v>31.2097595180061</v>
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.48478774391545</v>
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
         <v>23.10052348092744</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6227,7 +6227,7 @@
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.258981029111088</v>
+        <v>7.263040930263326</v>
       </c>
       <c r="C21" t="n">
-        <v>75.31192817702754</v>
+        <v>75.35404965148201</v>
       </c>
       <c r="D21" t="n">
-        <v>5.444235771833316</v>
+        <v>5.447280697697495</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.916191592240526</v>
+        <v>4.185190463204153</v>
       </c>
       <c r="C2" t="n">
-        <v>12.52611895848505</v>
+        <v>9.562222639363933</v>
       </c>
       <c r="D2" t="n">
-        <v>28.06816686441631</v>
+        <v>14.29130133072082</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.92394776288327</v>
+        <v>19.38460842035327</v>
       </c>
       <c r="C3" t="n">
-        <v>34.73914251477338</v>
+        <v>33.63958508601696</v>
       </c>
       <c r="D3" t="n">
-        <v>88.41619824446775</v>
+        <v>59.57735943221769</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.02242563294421</v>
+        <v>35.09748042682347</v>
       </c>
       <c r="C4" t="n">
-        <v>65.17921183264998</v>
+        <v>99.21738648659115</v>
       </c>
       <c r="D4" t="n">
-        <v>86.86307337634929</v>
+        <v>73.92167513896783</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.33033455917922</v>
+        <v>39.3680829402971</v>
       </c>
       <c r="C5" t="n">
-        <v>91.71977926925827</v>
+        <v>133.6158625479909</v>
       </c>
       <c r="D5" t="n">
-        <v>54.5606286635165</v>
+        <v>49.45554060143309</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.06169554111408</v>
+        <v>36.6290068454485</v>
       </c>
       <c r="C6" t="n">
-        <v>123.6530868452943</v>
+        <v>124.4581199627767</v>
       </c>
       <c r="D6" t="n">
-        <v>38.96360288614742</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>23.1162314441954</v>
       </c>
       <c r="C7" t="n">
-        <v>112.7065999429423</v>
+        <v>94.86039017514381</v>
       </c>
       <c r="D7" t="n">
-        <v>36.23139902522853</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>65.42366701100744</v>
+        <v>53.99121499505333</v>
       </c>
       <c r="D8" t="n">
         <v>33.46287049925253</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>32.39374724932775</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -6490,7 +6490,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>26.76244241776806</v>
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.460453093356549</v>
+        <v>7.464340795512516</v>
       </c>
       <c r="C21" t="n">
-        <v>83.93009730026118</v>
+        <v>83.97383394951581</v>
       </c>
       <c r="D21" t="n">
-        <v>6.527896456686981</v>
+        <v>6.531298196073451</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_26_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497633679118</v>
+        <v>10.84497605806098</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907195785489</v>
+        <v>37.78907098662589</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.696501090667494</v>
+        <v>1.076977231558751</v>
       </c>
       <c r="C2" t="n">
-        <v>6.346998907955629</v>
+        <v>2.54861704022472</v>
       </c>
       <c r="D2" t="n">
-        <v>21.18513370994192</v>
+        <v>12.69105257279852</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.61117115585603</v>
+        <v>8.035604959260143</v>
       </c>
       <c r="C3" t="n">
-        <v>35.38709599957628</v>
+        <v>32.43203540979338</v>
       </c>
       <c r="D3" t="n">
-        <v>57.1868037723767</v>
+        <v>74.82390127917066</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.79943003535994</v>
+        <v>12.22668590868978</v>
       </c>
       <c r="C4" t="n">
-        <v>91.27897455005143</v>
+        <v>99.25567464705678</v>
       </c>
       <c r="D4" t="n">
-        <v>85.66337768175968</v>
+        <v>90.98543198648164</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.60218086226435</v>
+        <v>10.62741889847172</v>
       </c>
       <c r="C5" t="n">
-        <v>156.981457909065</v>
+        <v>124.7065021319511</v>
       </c>
       <c r="D5" t="n">
-        <v>62.58641614573418</v>
+        <v>51.63992924338224</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.08185457901354</v>
+        <v>8.332092765942681</v>
       </c>
       <c r="C6" t="n">
-        <v>167.6883983715807</v>
+        <v>93.10208003683779</v>
       </c>
       <c r="D6" t="n">
-        <v>43.79380159104173</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.87774886752143</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>135.4635117273834</v>
+        <v>51.2030515149924</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.27385085622263</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>89.20650514638642</v>
+        <v>30.0414797499524</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>47.59218345877262</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.649775819534706</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.75353181185831</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.649775819534706</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.237444075707486</v>
+        <v>0.7304202919596269</v>
       </c>
       <c r="C2" t="n">
-        <v>6.225262192629025</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="D2" t="n">
-        <v>25.77284073188726</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.07535789351553</v>
+        <v>5.718680377237671</v>
       </c>
       <c r="C3" t="n">
-        <v>29.93348750248525</v>
+        <v>19.50732688338412</v>
       </c>
       <c r="D3" t="n">
-        <v>59.67062546412114</v>
+        <v>67.8240401478909</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.25964872447344</v>
+        <v>14.11556849166064</v>
       </c>
       <c r="C4" t="n">
-        <v>88.82853228025141</v>
+        <v>89.16036300428684</v>
       </c>
       <c r="D4" t="n">
-        <v>91.90434783765667</v>
+        <v>107.10474754251</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.81740459367266</v>
+        <v>14.50532233024663</v>
       </c>
       <c r="C5" t="n">
-        <v>161.8901964302991</v>
+        <v>157.5950502242192</v>
       </c>
       <c r="D5" t="n">
-        <v>76.35542769779569</v>
+        <v>71.37305809874313</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.20639766873265</v>
+        <v>11.35096695650162</v>
       </c>
       <c r="C6" t="n">
-        <v>202.3853257350715</v>
+        <v>147.5625704345211</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.33983324105218</v>
+        <v>7.665486074759095</v>
       </c>
       <c r="C7" t="n">
-        <v>182.1151808854876</v>
+        <v>92.70447221661782</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.03456645829366</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0962970282661</v>
+        <v>48.48361037422873</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.98124898262807</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>74.88280614142545</v>
+        <v>35.27812200440487</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>42.84837855185204</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.72012945549421</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.818314461441287</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.6607986910566</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.795603769121447</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.660397409788613</v>
+        <v>0.3848451000647496</v>
       </c>
       <c r="C2" t="n">
-        <v>7.880488821989147</v>
+        <v>2.863758053287946</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95799013736241</v>
+        <v>11.06331487915731</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.82286880707485</v>
+        <v>4.987278337573797</v>
       </c>
       <c r="C3" t="n">
-        <v>27.0864191601695</v>
+        <v>24.35225180384213</v>
       </c>
       <c r="D3" t="n">
-        <v>64.15230373400782</v>
+        <v>67.64732556112646</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.91054745238907</v>
+        <v>15.41736594749191</v>
       </c>
       <c r="C4" t="n">
-        <v>82.43440948249193</v>
+        <v>81.949426116594</v>
       </c>
       <c r="D4" t="n">
-        <v>98.20913159432968</v>
+        <v>116.2939060542602</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.74377351585415</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C5" t="n">
-        <v>160.4666622591412</v>
+        <v>179.9543541884404</v>
       </c>
       <c r="D5" t="n">
-        <v>86.78649705541805</v>
+        <v>80.47876805563229</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.19760299712343</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>222.9136702308723</v>
+        <v>187.5324647175215</v>
       </c>
       <c r="D6" t="n">
-        <v>60.49823877880121</v>
+        <v>39.32586778901449</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.94543270585223</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>225.7126329356799</v>
+        <v>87.1949041003847</v>
       </c>
       <c r="D7" t="n">
-        <v>45.33416373900496</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.04562772494764</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>176.0764507566654</v>
+        <v>43.0594543082651</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.08437354930299</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>108.6078032777119</v>
+        <v>26.18124777685393</v>
       </c>
       <c r="D9" t="n">
-        <v>36.16562192904399</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>60.64255569132548</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.970306710528112</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.5991405921295</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.96288338816014</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.728718838458391</v>
+        <v>0.5085453107998478</v>
       </c>
       <c r="C2" t="n">
-        <v>5.547856276698725</v>
+        <v>4.211697651218817</v>
       </c>
       <c r="D2" t="n">
-        <v>20.58135887183013</v>
+        <v>10.76486357706628</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.88101290580366</v>
+        <v>3.112140222462389</v>
       </c>
       <c r="C3" t="n">
-        <v>43.48160582109124</v>
+        <v>17.0529576227671</v>
       </c>
       <c r="D3" t="n">
-        <v>70.46985021083604</v>
+        <v>61.65866456522092</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.41959148480766</v>
+        <v>12.62233023350124</v>
       </c>
       <c r="C4" t="n">
-        <v>123.6197074233499</v>
+        <v>71.36913110792612</v>
       </c>
       <c r="D4" t="n">
-        <v>94.78872259273379</v>
+        <v>123.0453850163655</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.22586839190156</v>
+        <v>18.84955592153876</v>
       </c>
       <c r="C5" t="n">
-        <v>133.198619773686</v>
+        <v>166.9707407997763</v>
       </c>
       <c r="D5" t="n">
-        <v>58.63488163614076</v>
+        <v>101.3899941560894</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.99377502307181</v>
+        <v>14.04782790006761</v>
       </c>
       <c r="C6" t="n">
-        <v>148.6493651431223</v>
+        <v>237.0420014426882</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82647700272235</v>
+        <v>53.41394734495622</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>123.7856227853676</v>
+        <v>173.4316224414245</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.849694790259</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>80.02716411167874</v>
+        <v>75.77128781376882</v>
       </c>
       <c r="D8" t="n">
-        <v>26.62008900065226</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>46.26093357181394</v>
+        <v>37.82968428774233</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.71249645803847</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.60245859970483</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>27.8983245115816</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.14926670877452</v>
+        <v>0.2709623663721197</v>
       </c>
       <c r="C2" t="n">
-        <v>2.728276870101886</v>
+        <v>2.297289627937536</v>
       </c>
       <c r="D2" t="n">
-        <v>14.53968349989526</v>
+        <v>8.460701715199011</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.24840753137022</v>
+        <v>2.532909076956771</v>
       </c>
       <c r="C3" t="n">
-        <v>33.21743357319083</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="D3" t="n">
-        <v>71.49577656177397</v>
+        <v>57.63349897780901</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.62151271671301</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="C4" t="n">
-        <v>121.0161125116873</v>
+        <v>59.47427592327178</v>
       </c>
       <c r="D4" t="n">
-        <v>106.4538488145944</v>
+        <v>125.8404207303562</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>20.02765316663493</v>
       </c>
       <c r="C5" t="n">
-        <v>177.9417713947344</v>
+        <v>157.6195939168254</v>
       </c>
       <c r="D5" t="n">
-        <v>72.20754364735292</v>
+        <v>116.1407534123977</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.22649028670731</v>
+        <v>17.46921864936775</v>
       </c>
       <c r="C6" t="n">
-        <v>179.0796169839565</v>
+        <v>262.1590347081386</v>
       </c>
       <c r="D6" t="n">
-        <v>36.06548366321083</v>
+        <v>66.21397391292614</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4181557110055</v>
+        <v>236.1927896785146</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>40.06414206260808</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>105.2286276796944</v>
+        <v>115.1590057081509</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>50.36562072326985</v>
+        <v>49.58905828921062</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>32.59893251951534</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.899902791895831</v>
+        <v>0.7156940763959247</v>
       </c>
       <c r="C2" t="n">
-        <v>6.746570223584081</v>
+        <v>5.615596868291756</v>
       </c>
       <c r="D2" t="n">
-        <v>13.50393967191488</v>
+        <v>11.62192932287374</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.37403017978481</v>
+        <v>1.737693436516855</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71625921793945</v>
+        <v>12.72345024703866</v>
       </c>
       <c r="D3" t="n">
-        <v>66.85210992068656</v>
+        <v>51.67429041303086</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.64475586644545</v>
+        <v>7.65763209312512</v>
       </c>
       <c r="C4" t="n">
-        <v>102.1911002827547</v>
+        <v>50.82115165804039</v>
       </c>
       <c r="D4" t="n">
-        <v>116.1790415728633</v>
+        <v>125.9297597714426</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.35612204139689</v>
+        <v>18.4077694546277</v>
       </c>
       <c r="C5" t="n">
-        <v>198.9511722656162</v>
+        <v>135.9229696529709</v>
       </c>
       <c r="D5" t="n">
-        <v>90.34533248331273</v>
+        <v>131.9223477581652</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.29819892684633</v>
+        <v>21.57488754852791</v>
       </c>
       <c r="C6" t="n">
-        <v>227.8243722475149</v>
+        <v>258.0936174648525</v>
       </c>
       <c r="D6" t="n">
-        <v>47.41645061971246</v>
+        <v>83.20017269180445</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.10489244010094</v>
+        <v>12.57618809140164</v>
       </c>
       <c r="C7" t="n">
-        <v>203.3749274209522</v>
+        <v>303.2059062226976</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>47.66974152740813</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.93590866178347</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>152.0432669567035</v>
+        <v>200.1096345566274</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>41.64082887562846</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>83.20311793491715</v>
+        <v>87.52968006753285</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>43.70249905454677</v>
+        <v>42.99073196896783</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.975677291572082</v>
+        <v>0.4800746273766903</v>
       </c>
       <c r="C2" t="n">
-        <v>3.257438882690916</v>
+        <v>2.964878066825367</v>
       </c>
       <c r="D2" t="n">
-        <v>9.419869222248145</v>
+        <v>8.367435683295565</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.06477965294707</v>
+        <v>2.763619787454771</v>
       </c>
       <c r="C3" t="n">
-        <v>24.97075285751762</v>
+        <v>17.89726064841935</v>
       </c>
       <c r="D3" t="n">
-        <v>65.42366701100745</v>
+        <v>56.57812019574368</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.79263991688822</v>
+        <v>12.58404207303562</v>
       </c>
       <c r="C4" t="n">
-        <v>95.82250292530568</v>
+        <v>72.18594519785947</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6452328636603</v>
+        <v>129.9883047807989</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.04963683122264</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="C5" t="n">
-        <v>230.6125357275758</v>
+        <v>210.9039505648211</v>
       </c>
       <c r="D5" t="n">
-        <v>95.40133316018381</v>
+        <v>121.8594337896354</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>265.7011804250611</v>
+        <v>262.9238161697468</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>68.26680836250623</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>206.369257918905</v>
+        <v>140.7335334037803</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>36.29128563518759</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>105.9796646734432</v>
+        <v>64.50573290753667</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.72655972106742</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.7904711328347</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.645229225868407</v>
+        <v>0.2444551783574558</v>
       </c>
       <c r="C2" t="n">
-        <v>5.17086515826795</v>
+        <v>1.969385894719102</v>
       </c>
       <c r="D2" t="n">
-        <v>8.483281912396688</v>
+        <v>6.397068040872216</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.41482161500667</v>
+        <v>2.194206118991621</v>
       </c>
       <c r="C3" t="n">
-        <v>18.84955592153876</v>
+        <v>14.43169125242811</v>
       </c>
       <c r="D3" t="n">
-        <v>58.78214379177777</v>
+        <v>50.39801839751001</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.92928277422778</v>
+        <v>8.525497063679301</v>
       </c>
       <c r="C4" t="n">
-        <v>80.50723873905544</v>
+        <v>56.02834148136547</v>
       </c>
       <c r="D4" t="n">
-        <v>127.0145909846353</v>
+        <v>123.7345719047467</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.70159942230054</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C5" t="n">
-        <v>205.7743188101315</v>
+        <v>157.2023511425205</v>
       </c>
       <c r="D5" t="n">
-        <v>112.9991607588079</v>
+        <v>126.3263858439583</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.75354993516761</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>314.9289555591089</v>
+        <v>245.4545975203791</v>
       </c>
       <c r="D6" t="n">
-        <v>61.34352355215771</v>
+        <v>72.89574878802993</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.10382857693868</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C7" t="n">
-        <v>280.5088810482156</v>
+        <v>180.2586959767568</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>172.0709201233385</v>
+        <v>73.8519710519663</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>67.8937442348924</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>20.96718571959912</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>17.93653055658923</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.32722508515045</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.514255870576081</v>
+        <v>0.1335176877775662</v>
       </c>
       <c r="C2" t="n">
-        <v>3.292781800043802</v>
+        <v>6.56200165518568</v>
       </c>
       <c r="D2" t="n">
-        <v>6.32834570157494</v>
+        <v>6.568873889115409</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.88329519638165</v>
+        <v>1.448077863764045</v>
       </c>
       <c r="C3" t="n">
-        <v>19.56623174563893</v>
+        <v>10.465430527271</v>
       </c>
       <c r="D3" t="n">
-        <v>53.84395283941632</v>
+        <v>43.82030877905638</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.10046672766521</v>
+        <v>6.317546476828225</v>
       </c>
       <c r="C4" t="n">
-        <v>68.75277347610837</v>
+        <v>44.55465606183299</v>
       </c>
       <c r="D4" t="n">
-        <v>127.5889133916197</v>
+        <v>121.3734686760332</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.75760009917161</v>
+        <v>12.98361338866407</v>
       </c>
       <c r="C5" t="n">
-        <v>189.7963749235146</v>
+        <v>128.8543861823939</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5900750657732</v>
+        <v>142.8442909679109</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.24035792775378</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="C6" t="n">
-        <v>334.9742801844203</v>
+        <v>249.0369948931757</v>
       </c>
       <c r="D6" t="n">
-        <v>71.32593420893927</v>
+        <v>95.07441117466963</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>343.8090277749372</v>
+        <v>274.3405602224329</v>
       </c>
       <c r="D7" t="n">
-        <v>41.20198765183014</v>
+        <v>47.25053525769474</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>222.3069501496477</v>
+        <v>157.8846657969721</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>76.87968097186344</v>
+        <v>61.01561981893925</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>23.07499804061703</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.4519070435898</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>10.926851948267</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.259402378099411</v>
+        <v>0.450622196249286</v>
       </c>
       <c r="C2" t="n">
-        <v>11.19192382841364</v>
+        <v>8.499971623368884</v>
       </c>
       <c r="D2" t="n">
-        <v>12.42205370183489</v>
+        <v>12.53691818323177</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.85951226730147</v>
+        <v>0.9277515805132359</v>
       </c>
       <c r="C3" t="n">
-        <v>16.36573422979433</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D3" t="n">
-        <v>48.2479909252095</v>
+        <v>39.22082078466008</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>4.466952054322987</v>
       </c>
       <c r="C4" t="n">
-        <v>59.93373384885928</v>
+        <v>34.62525978108076</v>
       </c>
       <c r="D4" t="n">
-        <v>124.1429789497134</v>
+        <v>115.2218375612227</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.66571672559991</v>
+        <v>11.51099183229385</v>
       </c>
       <c r="C5" t="n">
-        <v>163.1664684458199</v>
+        <v>104.6052178874977</v>
       </c>
       <c r="D5" t="n">
-        <v>137.8619213688584</v>
+        <v>154.1343895667493</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.26302024040947</v>
+        <v>15.01386764104647</v>
       </c>
       <c r="C6" t="n">
-        <v>323.3415516367998</v>
+        <v>228.3073921180043</v>
       </c>
       <c r="D6" t="n">
-        <v>87.18508662334226</v>
+        <v>116.4882920997011</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.96137734883166</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>399.683234866736</v>
+        <v>319.4351775216017</v>
       </c>
       <c r="D7" t="n">
-        <v>48.38838084691679</v>
+        <v>61.50354842794993</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>312.4313893995049</v>
+        <v>258.9408657336174</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>34.71459882216722</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>146.1046750937145</v>
+        <v>125.1374893741154</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>25.29374785221481</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>50.67781649322036</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.65468685001238</v>
+        <v>2.737112599440108</v>
       </c>
       <c r="C2" t="n">
-        <v>10.89838126484384</v>
+        <v>13.8338069005418</v>
       </c>
       <c r="D2" t="n">
-        <v>9.447358157967058</v>
+        <v>14.25890365648067</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.358157985600839</v>
+        <v>0.4732023934469626</v>
       </c>
       <c r="C2" t="n">
-        <v>6.535494467171016</v>
+        <v>6.501133297522379</v>
       </c>
       <c r="D2" t="n">
-        <v>9.241191140075227</v>
+        <v>12.92274503100077</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.80613803837365</v>
+        <v>1.202640937702343</v>
       </c>
       <c r="C3" t="n">
-        <v>26.37956081311179</v>
+        <v>25.85923452986099</v>
       </c>
       <c r="D3" t="n">
-        <v>53.00455855228529</v>
+        <v>39.77550823755953</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.98408071921636</v>
+        <v>3.152391878336508</v>
       </c>
       <c r="C4" t="n">
-        <v>88.90510860118265</v>
+        <v>40.59821281371835</v>
       </c>
       <c r="D4" t="n">
-        <v>128.035608597052</v>
+        <v>109.5551898123101</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.61289797155305</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="C5" t="n">
-        <v>259.8686173141307</v>
+        <v>84.25849671698251</v>
       </c>
       <c r="D5" t="n">
-        <v>125.8109682992288</v>
+        <v>159.8039825587746</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.20003985195487</v>
+        <v>15.49688751153591</v>
       </c>
       <c r="C6" t="n">
-        <v>323.4623066044222</v>
+        <v>201.0167694353514</v>
       </c>
       <c r="D6" t="n">
-        <v>69.59511300635215</v>
+        <v>133.4342392227053</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.629341336151211</v>
+        <v>13.41460063082842</v>
       </c>
       <c r="C7" t="n">
-        <v>219.7239719397744</v>
+        <v>327.9989627457466</v>
       </c>
       <c r="D7" t="n">
-        <v>31.4404702285041</v>
+        <v>77.25372684718151</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>107.6486357706628</v>
+        <v>332.8762853404447</v>
       </c>
       <c r="D8" t="n">
-        <v>23.86628669023996</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>38.60624672180155</v>
+        <v>213.1109194039678</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>90.96383353698822</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>36.42774856607789</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>13.23494080095125</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.031677968443155</v>
+        <v>3.158282364561989</v>
       </c>
       <c r="C2" t="n">
-        <v>6.184028789050658</v>
+        <v>9.594620313604079</v>
       </c>
       <c r="D2" t="n">
-        <v>8.709083884373454</v>
+        <v>20.57939537642164</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>4.427682146153115</v>
       </c>
       <c r="C3" t="n">
-        <v>27.45948328778329</v>
+        <v>27.31222113214627</v>
       </c>
       <c r="D3" t="n">
-        <v>11.06920536538279</v>
+        <v>12.7283589855599</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39719586868497</v>
+        <v>11.67723083289473</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1382607242919</v>
+        <v>59.94311827552626</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576140690433526</v>
+        <v>0.7784820555263151</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.14337622254904</v>
+        <v>1.565887588273663</v>
       </c>
       <c r="C2" t="n">
-        <v>7.058765993534567</v>
+        <v>3.992767913171777</v>
       </c>
       <c r="D2" t="n">
-        <v>17.74410800655685</v>
+        <v>27.05107624281661</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.16924582022473</v>
+        <v>8.555931242510953</v>
       </c>
       <c r="C3" t="n">
-        <v>25.36836067773758</v>
+        <v>34.1206414610979</v>
       </c>
       <c r="D3" t="n">
-        <v>15.70796326794897</v>
+        <v>27.63619787454772</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.79948678862217</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C4" t="n">
-        <v>42.38499363544754</v>
+        <v>44.92477494633405</v>
       </c>
       <c r="D4" t="n">
-        <v>20.86704745376596</v>
+        <v>20.98191193516283</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43855983339176</v>
+        <v>13.62612288863908</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13091275471191</v>
+        <v>73.74137092675267</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250223122819317</v>
+        <v>1.603073281016362</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.486587008407923</v>
+        <v>1.443169125242811</v>
       </c>
       <c r="C2" t="n">
-        <v>10.6038569535698</v>
+        <v>7.180502708861171</v>
       </c>
       <c r="D2" t="n">
-        <v>30.28397143290136</v>
+        <v>24.87257808709294</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.14546289114455</v>
+        <v>6.828055283036567</v>
       </c>
       <c r="C3" t="n">
-        <v>26.60045404656733</v>
+        <v>22.3445777486574</v>
       </c>
       <c r="D3" t="n">
-        <v>26.25684235008094</v>
+        <v>43.6779553619406</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.62976760897449</v>
+        <v>12.07353326682727</v>
       </c>
       <c r="C4" t="n">
-        <v>54.21603521932585</v>
+        <v>70.04180821178444</v>
       </c>
       <c r="D4" t="n">
-        <v>24.05772749256809</v>
+        <v>30.59224021203486</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.00248757922301</v>
+        <v>5.816855147662352</v>
       </c>
       <c r="C5" t="n">
-        <v>46.92754026299754</v>
+        <v>51.81173509162543</v>
       </c>
       <c r="D5" t="n">
-        <v>30.16419821298325</v>
+        <v>27.4889357189107</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72794459720835</v>
+        <v>14.83228836637138</v>
       </c>
       <c r="C21" t="n">
-        <v>102.040462042971</v>
+        <v>87.34569815752037</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181986149302088</v>
+        <v>2.472048061061897</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.596943661911066</v>
+        <v>2.34245002233289</v>
       </c>
       <c r="C2" t="n">
-        <v>13.47645073619597</v>
+        <v>4.608323723734528</v>
       </c>
       <c r="D2" t="n">
-        <v>30.44988679491907</v>
+        <v>29.78328010373549</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.51928778228433</v>
+        <v>5.792311455056182</v>
       </c>
       <c r="C3" t="n">
-        <v>34.81768233111313</v>
+        <v>25.73651606683013</v>
       </c>
       <c r="D3" t="n">
-        <v>43.43251843587889</v>
+        <v>53.44143628067513</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.56519324467246</v>
+        <v>12.85205919629499</v>
       </c>
       <c r="C4" t="n">
-        <v>60.96751418143117</v>
+        <v>61.80985371167493</v>
       </c>
       <c r="D4" t="n">
-        <v>31.38352886165779</v>
+        <v>45.58843639440489</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.66765485881262</v>
+        <v>12.19821522526662</v>
       </c>
       <c r="C5" t="n">
-        <v>74.66191290796993</v>
+        <v>96.06401286055042</v>
       </c>
       <c r="D5" t="n">
-        <v>31.73499453977815</v>
+        <v>32.10314992887071</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.6050596854523</v>
+        <v>6.359761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>44.39757642915352</v>
+        <v>49.71079500453725</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>33.89189424600839</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04424074620395</v>
+        <v>16.06858559347762</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7171896299972</v>
+        <v>100.6400887170441</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014746915401315</v>
+        <v>3.382860124942658</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.735770998837365</v>
+        <v>1.863357142660446</v>
       </c>
       <c r="C2" t="n">
-        <v>11.05546089752333</v>
+        <v>7.187374942790899</v>
       </c>
       <c r="D2" t="n">
-        <v>23.20851572839459</v>
+        <v>27.49286270972768</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.32155558310322</v>
+        <v>6.970408700152354</v>
       </c>
       <c r="C3" t="n">
-        <v>41.91571823281757</v>
+        <v>21.25483779694344</v>
       </c>
       <c r="D3" t="n">
-        <v>53.5396110510998</v>
+        <v>64.18666490365646</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.24466046700248</v>
+        <v>11.92038062496477</v>
       </c>
       <c r="C4" t="n">
-        <v>62.97126124579891</v>
+        <v>62.61390508145308</v>
       </c>
       <c r="D4" t="n">
-        <v>39.55166976099125</v>
+        <v>61.22276858453534</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.85079971115027</v>
+        <v>15.87976911619216</v>
       </c>
       <c r="C5" t="n">
-        <v>69.72863069412972</v>
+        <v>105.8814899030185</v>
       </c>
       <c r="D5" t="n">
-        <v>28.91246989006857</v>
+        <v>40.39891802975625</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.49688751153591</v>
+        <v>11.39121861237574</v>
       </c>
       <c r="C6" t="n">
-        <v>55.8692983532775</v>
+        <v>103.0039873818711</v>
       </c>
       <c r="D6" t="n">
-        <v>30.47050349670826</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>27.18852092141116</v>
+        <v>45.21439051908685</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.047066446881602</v>
+        <v>17.32816292324548</v>
       </c>
       <c r="C21" t="n">
-        <v>66.06624793951502</v>
+        <v>114.3658752934202</v>
       </c>
       <c r="D21" t="n">
-        <v>4.404416529301002</v>
+        <v>4.33204073081137</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.310273332270997</v>
+        <v>2.207950586851076</v>
       </c>
       <c r="C2" t="n">
-        <v>7.023423076181681</v>
+        <v>10.17581495451819</v>
       </c>
       <c r="D2" t="n">
-        <v>16.90765896253857</v>
+        <v>23.17611805415445</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.82286880707485</v>
+        <v>6.587527095496097</v>
       </c>
       <c r="C3" t="n">
-        <v>42.70602513473625</v>
+        <v>24.74004214701962</v>
       </c>
       <c r="D3" t="n">
-        <v>60.09768571546849</v>
+        <v>70.32258805519903</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.18834099496192</v>
+        <v>12.52022847225957</v>
       </c>
       <c r="C4" t="n">
-        <v>89.04549852288996</v>
+        <v>57.63644422092175</v>
       </c>
       <c r="D4" t="n">
-        <v>58.42773287054467</v>
+        <v>77.6101012638231</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.57577148524092</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C5" t="n">
-        <v>97.85570242080085</v>
+        <v>109.6366748717626</v>
       </c>
       <c r="D5" t="n">
-        <v>36.79099521664922</v>
+        <v>51.78719139901926</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.08936440328224</v>
+        <v>16.02015903789946</v>
       </c>
       <c r="C6" t="n">
-        <v>87.74860980557993</v>
+        <v>135.1650604252924</v>
       </c>
       <c r="D6" t="n">
-        <v>33.2881194078966</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.11516758103314</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>57.85046522044755</v>
+        <v>94.92027678510286</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>28.53940576245478</v>
+        <v>41.80772598535042</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.263040930263326</v>
+        <v>17.71949314246887</v>
       </c>
       <c r="C21" t="n">
-        <v>75.35404965148201</v>
+        <v>127.5803506257758</v>
       </c>
       <c r="D21" t="n">
-        <v>5.447280697697495</v>
+        <v>5.31584794274066</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.185190463204153</v>
+        <v>1.990002596508285</v>
       </c>
       <c r="C2" t="n">
-        <v>9.562222639363933</v>
+        <v>6.348962403364123</v>
       </c>
       <c r="D2" t="n">
-        <v>14.29130133072082</v>
+        <v>18.43918538116359</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.38460842035327</v>
+        <v>8.59029241215959</v>
       </c>
       <c r="C3" t="n">
-        <v>33.63958508601696</v>
+        <v>40.36455686010761</v>
       </c>
       <c r="D3" t="n">
-        <v>59.57735943221769</v>
+        <v>76.32106652814704</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.09748042682347</v>
+        <v>8.155378179178253</v>
       </c>
       <c r="C4" t="n">
-        <v>99.21738648659115</v>
+        <v>90.13032973608269</v>
       </c>
       <c r="D4" t="n">
-        <v>73.92167513896783</v>
+        <v>70.98624950326987</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.3680829402971</v>
+        <v>9.007535186464487</v>
       </c>
       <c r="C5" t="n">
-        <v>133.6158625479909</v>
+        <v>80.74874867430016</v>
       </c>
       <c r="D5" t="n">
-        <v>49.45554060143309</v>
+        <v>38.97538385859838</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.6290068454485</v>
+        <v>6.359761628110839</v>
       </c>
       <c r="C6" t="n">
-        <v>124.4581199627767</v>
+        <v>62.51082157250717</v>
       </c>
       <c r="D6" t="n">
-        <v>37.15227837181205</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>5.210135066437822</v>
       </c>
       <c r="C7" t="n">
-        <v>94.86039017514381</v>
+        <v>29.34443887993716</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>53.99121499505333</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.464340795512516</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97383394951581</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531298196073451</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
